--- a/.export-validation/display/display.xlsx
+++ b/.export-validation/display/display.xlsx
@@ -10,23 +10,26 @@
     <sheet sheetId="4" name="4 Department Expenditure Review" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1 Department Expenditure Review'!$A1:$G35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1 Department Expenditure Review'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2 Department Expenditure Review'!$A1:$G35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2 Department Expenditure Review'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3 Department Expenditure Review'!$A1:$E35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3 Department Expenditure Review'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Department Expenditure Review'!$A1:$A6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'4 Department Expenditure Review'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1 Department Expenditure Review'!$A1:$G36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1 Department Expenditure Review'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2 Department Expenditure Review'!$A1:$G36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2 Department Expenditure Review'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'3 Department Expenditure Review'!$A1:$E36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3 Department Expenditure Review'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Department Expenditure Review'!$A1:$A7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'4 Department Expenditure Review'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="63">
   <si>
     <t>NORTHERN RAILWAY - MORADABAD DIVISION</t>
+  </si>
+  <si>
+    <t>Ordinary Working Expenses (OWE) PORTAL - Moradabad Division</t>
   </si>
   <si>
     <t>Department Expenditure Review - PU expenditure detail - columns 3-7</t>
@@ -621,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
@@ -671,205 +674,193 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="99" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4">
-        <v>48744</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3915</v>
-      </c>
-      <c r="E6" s="4">
-        <v>3939</v>
-      </c>
-      <c r="F6" s="4">
-        <v>4013</v>
-      </c>
-      <c r="G6" s="4">
-        <v>3849</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" s="4">
-        <v>28429</v>
+        <v>48744</v>
       </c>
       <c r="D7" s="4">
-        <v>2580</v>
+        <v>3915</v>
       </c>
       <c r="E7" s="4">
-        <v>2363</v>
+        <v>3939</v>
       </c>
       <c r="F7" s="4">
-        <v>2405</v>
+        <v>4013</v>
       </c>
       <c r="G7" s="4">
-        <v>2308</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="C8" s="4">
-        <v>1573</v>
+        <v>28429</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>2363</v>
       </c>
       <c r="F8" s="4">
-        <v>0</v>
+        <v>2405</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="4">
+        <v>1573</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4">
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4">
         <v>9805</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D10" s="4">
         <v>636</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E10" s="4">
         <v>641</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F10" s="4">
         <v>658</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G10" s="4">
         <v>623</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4">
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="4">
         <v>3644</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D11" s="4">
         <v>275</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E11" s="4">
         <v>276</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F11" s="4">
         <v>289</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G11" s="4">
         <v>272</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="4">
-        <v>31</v>
-      </c>
-      <c r="D11" s="4">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4">
-        <v>2</v>
-      </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>70</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="4">
+        <v>31</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="4">
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4">
         <v>124</v>
       </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
         <v>31</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="4">
-        <v>319</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -880,151 +871,151 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="4">
+        <v>319</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="4">
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4">
         <v>1727</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D15" s="4">
         <v>173</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E15" s="4">
         <v>211</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F15" s="4">
         <v>178</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G15" s="4">
         <v>198</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="16" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="4">
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="4">
         <v>568</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D16" s="4">
         <v>22</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E16" s="4">
         <v>89</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F16" s="4">
         <v>50</v>
       </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="4">
-        <v>120</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="C17" s="4">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D17" s="4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
       </c>
       <c r="F17" s="4">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="4">
+        <v>19</v>
+      </c>
+      <c r="D18" s="4">
+        <v>33</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>68</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="4">
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="4">
         <v>2488</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D19" s="4">
         <v>527</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E19" s="4">
         <v>95</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F19" s="4">
         <v>72</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G19" s="4">
         <v>247</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="4">
-        <v>0</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="C20" s="4">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
@@ -1041,13 +1032,13 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="C21" s="4">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -1064,79 +1055,79 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="4">
+        <v>169</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="4">
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="4">
         <v>42</v>
       </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="4">
+      <c r="B24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="4">
         <v>6020</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D24" s="4">
         <v>83</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E24" s="4">
         <v>53</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F24" s="4">
         <v>47</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G24" s="4">
         <v>187</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="4">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C25" s="4">
         <v>0</v>
@@ -1156,10 +1147,10 @@
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="C26" s="4">
         <v>0</v>
@@ -1179,79 +1170,79 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="4">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="4">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="4">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="4">
-        <v>0</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" s="4">
         <v>0</v>
@@ -1271,10 +1262,10 @@
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4">
         <v>0</v>
@@ -1294,10 +1285,10 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C32" s="4">
         <v>0</v>
@@ -1317,10 +1308,10 @@
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C33" s="4">
         <v>0</v>
@@ -1340,10 +1331,10 @@
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>
@@ -1363,33 +1354,57 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="4">
-        <v>0</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
+      <c r="B36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
         <v>15</v>
       </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4">
         <v>132</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1401,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
@@ -1420,7 +1435,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1431,7 +1446,7 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1451,61 +1466,49 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="99" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3946</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
+      <c r="G6" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" s="4">
-        <v>2367</v>
+        <v>3946</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -1522,13 +1525,13 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>2367</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
@@ -1545,59 +1548,59 @@
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4">
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4">
         <v>643</v>
       </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4">
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="4">
         <v>278</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
@@ -1614,36 +1617,36 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="4">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="4">
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4">
         <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="4">
-        <v>152</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
@@ -1660,59 +1663,59 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="4">
+        <v>152</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="4">
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4">
         <v>289</v>
       </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="4">
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="4">
         <v>53</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
@@ -1729,10 +1732,10 @@
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
@@ -1752,36 +1755,36 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="4">
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="4">
         <v>46</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="4">
-        <v>0</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
@@ -1798,13 +1801,13 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="C20" s="4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
@@ -1821,13 +1824,13 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="C21" s="4">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -1844,62 +1847,62 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="4">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="4">
+      <c r="B24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="4">
         <v>36</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D24" s="4">
         <v>32</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="4">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -1913,10 +1916,10 @@
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C25" s="4">
         <v>0</v>
@@ -1936,10 +1939,10 @@
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="C26" s="4">
         <v>0</v>
@@ -1959,79 +1962,79 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="4">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="4">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="4">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="4">
-        <v>0</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" s="4">
         <v>0</v>
@@ -2051,10 +2054,10 @@
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4">
         <v>0</v>
@@ -2074,10 +2077,10 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C32" s="4">
         <v>0</v>
@@ -2097,10 +2100,10 @@
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C33" s="4">
         <v>0</v>
@@ -2120,10 +2123,10 @@
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>
@@ -2143,33 +2146,57 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="4">
-        <v>0</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="B36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2181,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="18" customWidth="1"/>
@@ -2198,7 +2225,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2207,7 +2234,7 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2223,46 +2250,38 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="99" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
+      <c r="E6" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C7" s="4">
         <v>0</v>
@@ -2276,10 +2295,10 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
@@ -2293,44 +2312,44 @@
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="C11" s="4">
         <v>0</v>
@@ -2344,27 +2363,27 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="C13" s="4">
         <v>0</v>
@@ -2378,44 +2397,44 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C16" s="4">
         <v>0</v>
@@ -2429,10 +2448,10 @@
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
@@ -2446,27 +2465,27 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="4">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="C19" s="4">
         <v>0</v>
@@ -2480,10 +2499,10 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="C20" s="4">
         <v>0</v>
@@ -2497,10 +2516,10 @@
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="C21" s="4">
         <v>0</v>
@@ -2514,44 +2533,44 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="4">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="4">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="B24" s="3" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C24" s="4">
         <v>0</v>
@@ -2565,10 +2584,10 @@
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C25" s="4">
         <v>0</v>
@@ -2582,10 +2601,10 @@
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="C26" s="4">
         <v>0</v>
@@ -2599,61 +2618,61 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="4">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="4">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="4">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="4">
-        <v>0</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" s="4">
         <v>0</v>
@@ -2667,10 +2686,10 @@
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" s="4">
         <v>0</v>
@@ -2684,10 +2703,10 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C32" s="4">
         <v>0</v>
@@ -2701,10 +2720,10 @@
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C33" s="4">
         <v>0</v>
@@ -2718,10 +2737,10 @@
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>
@@ -2735,27 +2754,45 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="4">
-        <v>0</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
+      <c r="B36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2767,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -2780,12 +2817,12 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2794,13 +2831,18 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
+      <c r="A5" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/.export-validation/display/display.xlsx
+++ b/.export-validation/display/display.xlsx
@@ -716,19 +716,19 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>48744</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4">
-        <v>3915</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4">
-        <v>3939</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4">
-        <v>4013</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4">
-        <v>3849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -739,19 +739,19 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>28429</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4">
-        <v>2580</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4">
-        <v>2363</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4">
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>2308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -762,7 +762,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
@@ -785,19 +785,19 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>9805</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -808,19 +808,19 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>3644</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4">
-        <v>272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,19 +831,19 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -854,13 +854,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -900,19 +900,19 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>1727</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -923,16 +923,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -946,7 +946,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -969,16 +969,16 @@
         <v>35</v>
       </c>
       <c r="C18" s="4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
       </c>
       <c r="F18" s="4">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
@@ -992,19 +992,19 @@
         <v>37</v>
       </c>
       <c r="C19" s="4">
-        <v>2488</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4">
-        <v>247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="4">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="4">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>45</v>
       </c>
       <c r="C23" s="4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>47</v>
       </c>
       <c r="C24" s="4">
-        <v>6020</v>
+        <v>1</v>
       </c>
       <c r="D24" s="4">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1389,13 +1389,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
       </c>
       <c r="G36" s="4">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>3946</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>2367</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -1692,7 +1692,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
         <v>0</v>
@@ -1715,7 +1715,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
@@ -1784,7 +1784,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="4">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -1853,7 +1853,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>47</v>
       </c>
       <c r="C24" s="4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>

--- a/.export-validation/display/display.xlsx
+++ b/.export-validation/display/display.xlsx
@@ -716,19 +716,19 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>5</v>
+        <v>48744</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>3939</v>
       </c>
       <c r="F7" s="4">
-        <v>0</v>
+        <v>4013</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -739,19 +739,19 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>3</v>
+        <v>28429</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>2363</v>
       </c>
       <c r="F8" s="4">
-        <v>0</v>
+        <v>2405</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -762,7 +762,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>0</v>
+        <v>1573</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
@@ -785,19 +785,19 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>9805</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="F10" s="4">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -808,19 +808,19 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>0</v>
+        <v>3644</v>
       </c>
       <c r="D11" s="4">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="F11" s="4">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,19 +831,19 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -854,13 +854,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -900,19 +900,19 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>1727</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="F15" s="4">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -923,16 +923,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="D16" s="4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -946,7 +946,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -969,16 +969,16 @@
         <v>35</v>
       </c>
       <c r="C18" s="4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D18" s="4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
       </c>
       <c r="F18" s="4">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
@@ -992,19 +992,19 @@
         <v>37</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>2488</v>
       </c>
       <c r="D19" s="4">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F19" s="4">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G19" s="4">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="4">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="4">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>45</v>
       </c>
       <c r="C23" s="4">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>47</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>6020</v>
       </c>
       <c r="D24" s="4">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F24" s="4">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G24" s="4">
-        <v>0</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1389,13 +1389,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
       </c>
       <c r="G36" s="4">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>3946</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>2367</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -1692,7 +1692,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="D15" s="4">
         <v>0</v>
@@ -1715,7 +1715,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>37</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D19" s="4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>41</v>
       </c>
       <c r="C21" s="4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -1853,7 +1853,7 @@
         <v>43</v>
       </c>
       <c r="C22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>47</v>
       </c>
       <c r="C24" s="4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D24" s="4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>

--- a/.export-validation/display/display.xlsx
+++ b/.export-validation/display/display.xlsx
@@ -10,21 +10,21 @@
     <sheet sheetId="4" name="4 Department Expenditure Review" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1 Department Expenditure Review'!$A1:$G36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1 Department Expenditure Review'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2 Department Expenditure Review'!$A1:$G36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2 Department Expenditure Review'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3 Department Expenditure Review'!$A1:$E36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3 Department Expenditure Review'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Department Expenditure Review'!$A1:$A7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'4 Department Expenditure Review'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1 Department Expenditure Review'!$A1:$G38</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1 Department Expenditure Review'!$8:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2 Department Expenditure Review'!$A1:$G38</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2 Department Expenditure Review'!$8:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'3 Department Expenditure Review'!$A1:$E38</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3 Department Expenditure Review'!$8:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'4 Department Expenditure Review'!$A1:$A9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'4 Department Expenditure Review'!$8:$8</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="65">
   <si>
     <t>NORTHERN RAILWAY - MORADABAD DIVISION</t>
   </si>
@@ -35,10 +35,16 @@
     <t>Department Expenditure Review - PU expenditure detail - columns 3-7</t>
   </si>
   <si>
-    <t>Completed through AUG 2026; running SEP 2026</t>
-  </si>
-  <si>
-    <t>Displayed values and units; First 30 source detail records for layout testing. Rs thousands.</t>
+    <t>Reporting basis: Completed through AUG 2026; running month SEP 2026</t>
+  </si>
+  <si>
+    <t>Filters / search: PU Type: Staff | Search: salary</t>
+  </si>
+  <si>
+    <t>Sort order: Effective Budget descending</t>
+  </si>
+  <si>
+    <t>Generated: 23 Sept 2026, 10:00 pm; Source test-audit</t>
   </si>
   <si>
     <t>PU Code</t>
@@ -665,7 +671,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -718,7 +724,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" ht="138" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="73" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -729,300 +735,276 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" ht="86" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" s="6">
-        <v>48744</v>
-      </c>
-      <c r="D7" s="6">
-        <v>3915</v>
-      </c>
-      <c r="E7" s="6">
-        <v>3939</v>
-      </c>
-      <c r="F7" s="6">
-        <v>4013</v>
-      </c>
-      <c r="G7" s="6">
-        <v>3849</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6">
-        <v>28429</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2580</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2363</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2405</v>
-      </c>
-      <c r="G8" s="6">
-        <v>2308</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6">
-        <v>1573</v>
+        <v>48744</v>
       </c>
       <c r="D9" s="6">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="E9" s="6">
-        <v>0</v>
+        <v>3939</v>
       </c>
       <c r="F9" s="6">
-        <v>0</v>
+        <v>4013</v>
       </c>
       <c r="G9" s="6">
-        <v>0</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>28429</v>
+      </c>
+      <c r="D10" s="6">
+        <v>2580</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2363</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2405</v>
+      </c>
+      <c r="G10" s="6">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="6">
+        <v>1573</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6">
         <v>9805</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D12" s="6">
         <v>636</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E12" s="6">
         <v>641</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F12" s="6">
         <v>658</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G12" s="6">
         <v>623</v>
       </c>
     </row>
-    <row r="11" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6">
+    <row r="13" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="6">
         <v>3644</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D13" s="6">
         <v>275</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E13" s="6">
         <v>276</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F13" s="6">
         <v>289</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G13" s="6">
         <v>272</v>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="6">
+        <v>31</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2</v>
+      </c>
+      <c r="G14" s="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="6">
+        <v>124</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>31</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="6">
+        <v>319</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1727</v>
+      </c>
+      <c r="D17" s="6">
+        <v>173</v>
+      </c>
+      <c r="E17" s="6">
+        <v>211</v>
+      </c>
+      <c r="F17" s="6">
+        <v>178</v>
+      </c>
+      <c r="G17" s="6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="6">
+        <v>568</v>
+      </c>
+      <c r="D18" s="6">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="6">
-        <v>31</v>
-      </c>
-      <c r="D12" s="6">
-        <v>2</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6">
-        <v>2</v>
-      </c>
-      <c r="G12" s="6">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="6">
-        <v>124</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>31</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="6">
-        <v>319</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1727</v>
-      </c>
-      <c r="D15" s="6">
-        <v>173</v>
-      </c>
-      <c r="E15" s="6">
-        <v>211</v>
-      </c>
-      <c r="F15" s="6">
-        <v>178</v>
-      </c>
-      <c r="G15" s="6">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="6">
-        <v>568</v>
-      </c>
-      <c r="D16" s="6">
-        <v>22</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="E18" s="6">
         <v>89</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F18" s="6">
         <v>50</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="6">
-        <v>120</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="6">
-        <v>19</v>
-      </c>
-      <c r="D18" s="6">
-        <v>33</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
-        <v>68</v>
       </c>
       <c r="G18" s="6">
         <v>0</v>
@@ -1030,194 +1012,194 @@
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="6">
+        <v>120</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
+        <v>19</v>
+      </c>
+      <c r="D20" s="6">
+        <v>33</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>68</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="6">
         <v>2488</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D21" s="6">
         <v>527</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E21" s="6">
         <v>95</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F21" s="6">
         <v>72</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G21" s="6">
         <v>247</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="6">
-        <v>208</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C23" s="6">
+        <v>208</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="6">
         <v>169</v>
       </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="6">
         <v>42</v>
       </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="6">
+        <v>6020</v>
+      </c>
+      <c r="D26" s="6">
+        <v>83</v>
+      </c>
+      <c r="E26" s="6">
+        <v>53</v>
+      </c>
+      <c r="F26" s="6">
         <v>47</v>
       </c>
-      <c r="C24" s="6">
-        <v>6020</v>
-      </c>
-      <c r="D24" s="6">
-        <v>83</v>
-      </c>
-      <c r="E24" s="6">
-        <v>53</v>
-      </c>
-      <c r="F24" s="6">
-        <v>47</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="G26" s="6">
         <v>187</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C27" s="6">
         <v>0</v>
@@ -1237,56 +1219,56 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="6">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="C29" s="6">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C30" s="6">
         <v>0</v>
@@ -1306,10 +1288,10 @@
     </row>
     <row r="31" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
@@ -1329,10 +1311,10 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C32" s="6">
         <v>0</v>
@@ -1352,10 +1334,10 @@
     </row>
     <row r="33" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C33" s="6">
         <v>0</v>
@@ -1375,10 +1357,10 @@
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" s="6">
         <v>0</v>
@@ -1398,10 +1380,10 @@
     </row>
     <row r="35" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C35" s="6">
         <v>0</v>
@@ -1421,10 +1403,10 @@
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C36" s="6">
         <v>0</v>
@@ -1433,25 +1415,73 @@
         <v>0</v>
       </c>
       <c r="E36" s="6">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6">
         <v>15</v>
       </c>
-      <c r="F36" s="6">
-        <v>0</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6">
         <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:G36"/>
-  <mergeCells count="5">
+  <autoFilter ref="A8:G38"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.35" top="0.5" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LFor Official Use Only&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -1464,7 +1494,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1496,7 +1526,7 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1516,7 +1546,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" ht="138" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="73" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1527,84 +1557,60 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" ht="86" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="6">
-        <v>3946</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2367</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
+      <c r="F8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6">
-        <v>0</v>
+        <v>3946</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
@@ -1621,197 +1627,197 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2367</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6">
         <v>643</v>
       </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="6">
         <v>278</v>
       </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="6">
         <v>2</v>
       </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="6">
         <v>1</v>
       </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="6">
         <v>152</v>
       </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6">
         <v>289</v>
       </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="6">
         <v>53</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0</v>
       </c>
       <c r="D18" s="6">
         <v>0</v>
@@ -1828,62 +1834,62 @@
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="6">
         <v>46</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D21" s="6">
         <v>46</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="6">
-        <v>65</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
       </c>
       <c r="E21" s="6">
         <v>0</v>
@@ -1897,108 +1903,108 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C23" s="6">
+        <v>65</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="6">
         <v>36</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D26" s="6">
         <v>49</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
       </c>
       <c r="E26" s="6">
         <v>0</v>
@@ -2012,10 +2018,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C27" s="6">
         <v>0</v>
@@ -2035,56 +2041,56 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="6">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="C29" s="6">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C30" s="6">
         <v>0</v>
@@ -2104,10 +2110,10 @@
     </row>
     <row r="31" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
@@ -2127,10 +2133,10 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C32" s="6">
         <v>0</v>
@@ -2150,10 +2156,10 @@
     </row>
     <row r="33" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C33" s="6">
         <v>0</v>
@@ -2173,10 +2179,10 @@
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" s="6">
         <v>0</v>
@@ -2196,10 +2202,10 @@
     </row>
     <row r="35" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C35" s="6">
         <v>0</v>
@@ -2219,10 +2225,10 @@
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C36" s="6">
         <v>0</v>
@@ -2240,16 +2246,64 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37" ht="47" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:G36"/>
-  <mergeCells count="5">
+  <autoFilter ref="A8:G38"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.35" top="0.5" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LFor Official Use Only&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -2262,7 +2316,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2290,7 +2344,7 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2306,7 +2360,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" ht="138" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" ht="73" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -2315,63 +2369,47 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="60" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" ht="86" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
+      <c r="D8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6">
         <v>0</v>
@@ -2385,146 +2423,146 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="C14" s="6">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="6">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="C15" s="6">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="C16" s="6">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="C18" s="6">
         <v>0</v>
@@ -2538,44 +2576,44 @@
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="C21" s="6">
         <v>0</v>
@@ -2589,62 +2627,62 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="6">
-        <v>0</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="C24" s="6">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="6">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="C25" s="6">
         <v>0</v>
       </c>
@@ -2655,12 +2693,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C26" s="6">
         <v>0</v>
@@ -2674,10 +2712,10 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C27" s="6">
         <v>0</v>
@@ -2691,44 +2729,44 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="6">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="C29" s="6">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C30" s="6">
         <v>0</v>
@@ -2742,10 +2780,10 @@
     </row>
     <row r="31" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
@@ -2759,10 +2797,10 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C32" s="6">
         <v>0</v>
@@ -2776,10 +2814,10 @@
     </row>
     <row r="33" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C33" s="6">
         <v>0</v>
@@ -2793,10 +2831,10 @@
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" s="6">
         <v>0</v>
@@ -2810,10 +2848,10 @@
     </row>
     <row r="35" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C35" s="6">
         <v>0</v>
@@ -2827,10 +2865,10 @@
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C36" s="6">
         <v>0</v>
@@ -2842,16 +2880,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37" ht="47" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:E36"/>
-  <mergeCells count="5">
+  <autoFilter ref="A8:E38"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.35" top="0.5" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LFor Official Use Only&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -2864,7 +2938,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -2882,7 +2956,7 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2890,24 +2964,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>61</v>
+      <c r="A6" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>62</v>
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:A7"/>
-  <pageMargins left="0.35" right="0.35" top="0.5" bottom="0.45" header="0.2" footer="0.2"/>
+  <autoFilter ref="A8:A9"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LFor Official Use Only&amp;RPage &amp;P of &amp;N</oddFooter>

--- a/.export-validation/display/display.xlsx
+++ b/.export-validation/display/display.xlsx
@@ -1613,7 +1613,7 @@
         <v>3946</v>
       </c>
       <c r="D9" s="6">
-        <v>0</v>
+        <v>4056</v>
       </c>
       <c r="E9" s="6">
         <v>0</v>
@@ -1636,7 +1636,7 @@
         <v>2367</v>
       </c>
       <c r="D10" s="6">
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="E10" s="6">
         <v>0</v>
@@ -1682,7 +1682,7 @@
         <v>643</v>
       </c>
       <c r="D12" s="6">
-        <v>0</v>
+        <v>671</v>
       </c>
       <c r="E12" s="6">
         <v>0</v>
@@ -1705,7 +1705,7 @@
         <v>278</v>
       </c>
       <c r="D13" s="6">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="E13" s="6">
         <v>0</v>
@@ -1728,7 +1728,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>152</v>
       </c>
       <c r="D16" s="6">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="E16" s="6">
         <v>0</v>
@@ -1797,7 +1797,7 @@
         <v>289</v>
       </c>
       <c r="D17" s="6">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
@@ -1820,7 +1820,7 @@
         <v>53</v>
       </c>
       <c r="D18" s="6">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>46</v>
       </c>
       <c r="D21" s="6">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E21" s="6">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>36</v>
       </c>
       <c r="D26" s="6">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="E26" s="6">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E33" s="6">
         <v>0</v>

--- a/.export-validation/display/display.xlsx
+++ b/.export-validation/display/display.xlsx
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="6">
-        <v>0</v>
+        <v>1424</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>72</v>
       </c>
       <c r="E21" s="6">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="F21" s="6">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>83</v>
       </c>
       <c r="E26" s="6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F26" s="6">
         <v>0</v>
